--- a/artfynd/A 70301-2021 artfynd.xlsx
+++ b/artfynd/A 70301-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 70301-2021 artfynd.xlsx
+++ b/artfynd/A 70301-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104308164</v>
+        <v>104308159</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409914.47411661</v>
+        <v>409985</v>
       </c>
       <c r="R2" t="n">
-        <v>6715843.744918558</v>
+        <v>6715938</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104308161</v>
+        <v>104308160</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409950.4477421287</v>
+        <v>409973</v>
       </c>
       <c r="R3" t="n">
-        <v>6715903.342127105</v>
+        <v>6715907</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104308160</v>
+        <v>104308161</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409973.7098246352</v>
+        <v>409951</v>
       </c>
       <c r="R4" t="n">
-        <v>6715907.679452286</v>
+        <v>6715903</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>104308163</v>
       </c>
       <c r="B5" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409916.1097727959</v>
+        <v>409916</v>
       </c>
       <c r="R5" t="n">
-        <v>6715869.771548135</v>
+        <v>6715870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,16 +1066,11 @@
         <v>104308162</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409944.9216442591</v>
+        <v>409945</v>
       </c>
       <c r="R6" t="n">
-        <v>6715899.053670175</v>
+        <v>6715899</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,16 +1163,11 @@
         <v>104308165</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409868.2960869511</v>
+        <v>409869</v>
       </c>
       <c r="R7" t="n">
-        <v>6715770.138453186</v>
+        <v>6715770</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2022-08-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,6 +1254,103 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104308164</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Åskakskölen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>409914</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6715844</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 70301-2021 artfynd.xlsx
+++ b/artfynd/A 70301-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308160</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308161</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308163</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308162</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308165</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,8 +1386,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104308164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>